--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90220</v>
+        <v>90230</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90230</v>
+        <v>90242</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90242</v>
+        <v>90243</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90243</v>
+        <v>90246</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90246</v>
+        <v>90252</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -7292,7 +7292,7 @@
         <v>111646147</v>
       </c>
       <c r="B59" t="n">
-        <v>90252</v>
+        <v>90253</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9389,6 +9389,113 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126295056</v>
+      </c>
+      <c r="B78" t="n">
+        <v>105356</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Bye kalkbarrskogs naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>485429</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6995865</v>
+      </c>
+      <c r="S78" t="n">
+        <v>15</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Marieby</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:53</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -9394,7 +9394,7 @@
         <v>126295056</v>
       </c>
       <c r="B78" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -9394,7 +9394,7 @@
         <v>126295056</v>
       </c>
       <c r="B78" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 60950-2019 artfynd.xlsx
+++ b/artfynd/A 60950-2019 artfynd.xlsx
@@ -9394,7 +9394,7 @@
         <v>126295056</v>
       </c>
       <c r="B78" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
